--- a/questionari/risposte/Nasa Task Load Index - VISIONARY (Responses).xlsx
+++ b/questionari/risposte/Nasa Task Load Index - VISIONARY (Responses).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Timestamp</t>
   </si>
@@ -35,12 +35,36 @@
   </si>
   <si>
     <t>FRUSTRATION LEVEL: How insecure, discouraged, irritated, stressed and annoyed versus secure, gratified, content, relaxed and complacent did you feel during the task? (please choosing a number from 1 to 20 where 1= low and 20= high .)</t>
+  </si>
+  <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>S002</t>
+  </si>
+  <si>
+    <t>S003</t>
+  </si>
+  <si>
+    <t>S004</t>
+  </si>
+  <si>
+    <t>S005</t>
+  </si>
+  <si>
+    <t>S006</t>
+  </si>
+  <si>
+    <t>S007</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="10.0"/>
@@ -68,12 +92,24 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -154,23 +190,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:H1" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H8" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="8">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
+    <tableColumn name="Timestamp" id="1"/>
+    <tableColumn name="ID" id="2"/>
+    <tableColumn name="MENTAL DEMAND: How much mental and perceptual activity was required (e.g., thinking, deciding, calculating, remembering, looking, searching, etc.)? Was the task easy or demanding, simple or complex, exacting or forgiving? (please choosing a number from 1 to 20 where 1= low and 20= high.)" id="3"/>
+    <tableColumn name="PHYSICAL DEMAND: How much physical activity was required? (e.g, pushing, pulling, turning, controlling, activating, etc.)? Was the task easy or demanding, slow or brisk, slack or strenuous, restful or laborious? (please choosing a number from 1 to 20 where 1= low and 20= high.)" id="4"/>
+    <tableColumn name="TEMPORAL DEMAND: How much time pressure did you feel due to the rate or pace at which the tasks occurred? Was the pace slow and leisurely or rapid and frantic? (please choosing a number from 1 to 20 where1= low and 20= high.)" id="5"/>
+    <tableColumn name="PERFORMANCE: How successful do you think you were in accomplishing the goals of the task set by the experimenter (or yourself)? How satisfied were you with your performance in accomplishing these goals? (please choosing a number from 1 to 20 where 1= low and 20= high.)" id="6"/>
+    <tableColumn name="EFFORT: How hard did you have to work (mentally and physically) to accomplish your level of performance? (please choosing a number from 1 to 20 where 1= low and 20= high.)" id="7"/>
+    <tableColumn name="FRUSTRATION LEVEL: How insecure, discouraged, irritated, stressed and annoyed versus secure, gratified, content, relaxed and complacent did you feel during the task? (please choosing a number from 1 to 20 where 1= low and 20= high .)" id="8"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
-    </ext>
-  </extLst>
 </table>
 </file>
 
@@ -406,6 +437,188 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="2">
+        <v>46294.81877329861</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="4">
+        <v>46295.444506597225</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="4">
+        <v>46295.50053878472</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>18.0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="4">
+        <v>46295.5523368287</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="4">
+        <v>46295.65882532408</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="4">
+        <v>46295.71786856481</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>18.0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="4">
+        <v>46295.75939864584</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>13.0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>8.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
   <tableParts count="1">

--- a/questionari/risposte/Nasa Task Load Index - VISIONARY (Responses).xlsx
+++ b/questionari/risposte/Nasa Task Load Index - VISIONARY (Responses).xlsx
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:H7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:H12" headerRowCount="1">
   <tableColumns count="8">
     <tableColumn id="1" name="Timestamp"/>
     <tableColumn id="2" name="ID"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.88" customWidth="1" style="6" min="1" max="2"/>
@@ -634,7 +634,146 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1" s="6"/>
+    <row r="8" ht="22.5" customHeight="1" s="6">
+      <c r="A8" s="4" t="n">
+        <v>46296.48218760417</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>S007</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1" s="6">
+      <c r="A9" s="4" t="n">
+        <v>46296.53373622685</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" s="6">
+      <c r="A10" s="4" t="n">
+        <v>46296.63779658564</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>S009</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1" s="6">
+      <c r="A11" s="4" t="n">
+        <v>46296.68531568287</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1" s="6">
+      <c r="A12" s="4" t="n">
+        <v>46296.73167770833</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/questionari/risposte/Nasa Task Load Index - VISIONARY (Responses).xlsx
+++ b/questionari/risposte/Nasa Task Load Index - VISIONARY (Responses).xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.88" customWidth="1" style="6" min="1" max="2"/>
@@ -636,7 +636,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1" s="6">
       <c r="A8" s="4" t="n">
-        <v>46296.48218760417</v>
+        <v>46296.53373622685</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -644,27 +644,27 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="G8" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" s="6">
       <c r="A9" s="4" t="n">
-        <v>46296.53373622685</v>
+        <v>46296.63779658564</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -672,27 +672,27 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" s="6">
       <c r="A10" s="4" t="n">
-        <v>46296.63779658564</v>
+        <v>46296.68531568287</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -700,27 +700,27 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1" s="6">
       <c r="A11" s="4" t="n">
-        <v>46296.68531568287</v>
+        <v>46296.73167770833</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -728,52 +728,25 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>10</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1" s="6">
-      <c r="A12" s="4" t="n">
-        <v>46296.73167770833</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>S011</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>5</v>
-      </c>
-    </row>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1" s="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
